--- a/2026년 국내 생산 요청 수량 리스트.xlsx
+++ b/2026년 국내 생산 요청 수량 리스트.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\09.AI_Columbus_2025\2.AI\29.국내 제품 용마출고 관리 시스템\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5578812A-2548-484C-858C-3DD2B9714D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4440B736-9724-4BC3-B752-1A7E596075CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4290" yWindow="2460" windowWidth="38640" windowHeight="19140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6735,7 +6735,8 @@
   <cols>
     <col min="4" max="4" width="12.625" customWidth="1"/>
     <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.875" customWidth="1"/>
+    <col min="7" max="7" width="14.625" customWidth="1"/>
     <col min="8" max="8" width="40.375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" bestFit="1" customWidth="1"/>
     <col min="10" max="12" width="18.75" bestFit="1" customWidth="1"/>
